--- a/data/trans_dic/P1438_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1438_2023-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,45; 12,96</t>
+          <t>7,81; 12,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,19; 20,18</t>
+          <t>15,78; 19,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,48; 16,6</t>
+          <t>13,05; 16,06</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,61; 4,64</t>
+          <t>3,36; 4,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,16; 6,72</t>
+          <t>5,61; 7,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,74; 5,34</t>
+          <t>4,7; 5,84</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,64</t>
+          <t>1,4; 3,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 5,11</t>
+          <t>2,92; 5,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,03</t>
+          <t>2,52; 4,11</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,45; 5,16</t>
+          <t>4,03; 5,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,53; 8,76</t>
+          <t>7,82; 9,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,37; 6,77</t>
+          <t>6,19; 7,11</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>53547</t>
+          <t>56192</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>136293</t>
+          <t>146302</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>189841</t>
+          <t>202493</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>43340; 66488</t>
+          <t>45016; 70252</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>121940; 152024</t>
+          <t>129605; 163681</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>170647; 210137</t>
+          <t>182360; 224502</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>84054</t>
+          <t>90826</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>125479</t>
+          <t>140366</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>209533</t>
+          <t>231191</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>59689; 106205</t>
+          <t>74919; 109510</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>93131; 150238</t>
+          <t>121754; 160738</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>169208; 241819</t>
+          <t>206763; 256827</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15127</t>
+          <t>16711</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25722</t>
+          <t>29764</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40848</t>
+          <t>46476</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8890; 23489</t>
+          <t>9939; 26098</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18190; 33747</t>
+          <t>21442; 39009</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30339; 52624</t>
+          <t>36392; 59427</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>152728</t>
+          <t>163729</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>287494</t>
+          <t>316432</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>440222</t>
+          <t>480161</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>118971; 178099</t>
+          <t>141708; 188665</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>238221; 319625</t>
+          <t>291257; 344331</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>381254; 480689</t>
+          <t>448317; 515155</t>
         </is>
       </c>
     </row>
